--- a/2_RPA_basic_Python/1_excel/samples/RPA_XLS/sample.xlsx
+++ b/2_RPA_basic_Python/1_excel/samples/RPA_XLS/sample.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C2" t="n">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -462,13 +462,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="C5" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C6" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D7" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
@@ -542,13 +542,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
